--- a/06-normatividad/checklist-cliente.xlsx
+++ b/06-normatividad/checklist-cliente.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,17 +28,41 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0008427B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,14 +70,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -421,13 +470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -474,7 +524,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Se informa a estudiantes/docentes la finalidad del uso de sus horarios y correos para la logística de la encuesta.</t>
+          <t>Los correos que se envían a los profesores informan la finalidad del uso de sus datos (horario, clase, correo) para la logística de la encuesta.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -484,12 +534,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La Política de Tratamiento de Datos Personales de la Universidad (vigente desde 2013, Num. 4-a y Num. 7) obliga a informar la finalidad antes o al momento de recolectar el dato, pero no se encontró evidencia de que el mensaje de notificación del flujo de Power Automate (Cruce de Horarios / Notificación a Profesores) incluya un aviso de privacidad específico de este proceso.</t>
+          <t>La política de tratamiento de datos de la universidad (Num. 4-a y Num. 7) exige informar la finalidad al recolectar el dato. Hoy los avisos se escriben a mano en Outlook (hallazgo H5 del Taller 4) y no se encontró una plantilla con aviso de privacidad.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Incluir en el cuerpo del correo/notificación un aviso de privacidad breve citando la finalidad puntual (programación y aplicación de la encuesta de satisfacción) y el fundamento legal (Ley 1581 de 2012, Política institucional).</t>
+          <t>Crear una plantilla de aviso con un párrafo breve de finalidad (programación de la encuesta) y el fundamento (Ley 1581 de 2012 y política institucional).</t>
         </is>
       </c>
     </row>
@@ -504,7 +554,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Existe canal visible para que estudiantes/docentes consulten o se opongan al uso de sus datos en este proceso.</t>
+          <t>Los profesores y estudiantes conocen el canal para consultar, corregir u oponerse al uso de sus datos en este proceso (derechos de acceso, actualización, rectificación y supresión).</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -514,12 +564,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La política institucional define un procedimiento formal de PQR (Num. 10, plazo máximo 15 días hábiles), pero no se evidenció que la comunicación enviada a estudiantes/profesores en este proceso referencie explícitamente ese canal.</t>
+          <t>La política define el procedimiento de PQR (Num. 5 y Num. 10, respuesta en 15 días hábiles) y las áreas responsables (Registro Académico para estudiantes, Desarrollo Humano para empleados), pero los avisos del proceso no lo mencionan.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Agregar al pie de la notificación el canal institucional de PQR de datos personales y el enlace a la política vigente.</t>
+          <t>Incluir al pie de la plantilla el canal protecciondedatos@unisabana.edu.co y el enlace a la política vigente.</t>
         </is>
       </c>
     </row>
@@ -529,12 +579,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Protección de Datos (Horarios)</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>El cruce/consolidación de horarios de estudiantes respeta el principio de finalidad y no se reutiliza para otros fines.</t>
+          <t>Los datos exportados de SIGA se usan solo para la encuesta y no se reutilizan en otros reportes (principio de finalidad).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -544,12 +594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>El principio de finalidad (Num. 4-a de la política) prohíbe reutilizar el dato para fines distintos a los informados, pero no se confirmó con el cliente si los horarios cruzados desde SIGA se usan únicamente para la encuesta o si se reutilizan en otros reportes (p. ej. Power BI institucional).</t>
+          <t>El principio de finalidad (Num. 4-a) prohíbe reutilizar el dato para fines distintos. No se confirmó si las hojas o las exportaciones se reutilizan para otros reportes (pregunta P4).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Documentar explícitamente en el flujo (o en un anexo del proceso) que los horarios cruzados se usan únicamente para la programación de la encuesta, y verificar que no exista reutilización en otros tableros.</t>
+          <t>Dejar por escrito, en la primera pestaña de cada hoja, la finalidad del archivo y que no debe usarse para otros fines.</t>
         </is>
       </c>
     </row>
@@ -559,12 +609,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Protección de Datos (Horarios)</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>El acceso a los horarios está restringido a los roles que administran la logística de la encuesta.</t>
+          <t>La exportación de SIGA incluye solo los campos necesarios para la muestra y la asignación (minimización).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -574,12 +624,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>No se tuvo acceso a la configuración real de permisos del sitio de SharePoint que aloja el Repositorio de Programación; este mismo hallazgo quedó documentado como riesgo Alto (T1) en el análisis STRIDE del Taller 5.</t>
+          <t>La coordinadora tiene acceso en SIGA a horarios, correos y datos personales (Taller 4, H2) y las exportaciones se cargan a las hojas sin filtrar columnas. Ver amenaza T7 del Taller 5.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Definir y documentar una matriz de roles y permisos (RBAC) en SharePoint/Power Platform limitada al equipo de Automatización y al Coordinador de Encuestas.</t>
+          <t>Definir la lista mínima de columnas (p. ej. código, programa, semestre, clase, horario, correo del profesor) y borrar las demás antes de cargar a las hojas.</t>
         </is>
       </c>
     </row>
@@ -589,27 +639,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Correos Institucionales</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>El envío de notificaciones obligatorias a profesores usa el correo institucional autenticado y queda trazado.</t>
+          <t>El acceso a la Hoja de Muestreo y a la Hoja de Asignación PAT en OneDrive está restringido a las personas que operan el proceso.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>✅ Cumple</t>
+          <t>⚠️ Parcial</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Power Automate exige autenticación OAuth con la cuenta de conexión institucional del conector de Office 365 Outlook / Exchange Online; no admite envío anónimo ni cuentas externas sin autorización del tenant. Además, cada ejecución del flujo de notificación queda registrada automáticamente en el historial de ejecuciones (Run History) de Power Automate, con fecha, estado y detalle de cada paso — trazabilidad nativa de la plataforma, sin configuración adicional.</t>
+          <t>Las hojas están en el OneDrive de la cuenta institucional de la coordinadora (confirmado, Taller 4). No se confirmó quién más tiene acceso (pregunta P2). Ver amenaza T1 (riesgo Alto).</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Exportar periódicamente el historial de ejecuciones a un registro de auditoría de largo plazo, ya que Power Automate conserva el historial de ejecuciones solo por un periodo limitado por defecto.</t>
+          <t>Revisar "Administrar acceso" en cada hoja y dejar solo a la coordinadora y a su persona de respaldo.</t>
         </is>
       </c>
     </row>
@@ -619,12 +669,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Correos Institucionales</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Existe un reglamento o política publicada sobre el uso adecuado del correo institucional.</t>
+          <t>Las hojas se comparten solo con personas específicas, sin enlaces de tipo "Cualquier persona" ni "Personas de la organización".</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -634,12 +684,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>No se encontró un reglamento o política institucional publicada específicamente sobre el uso adecuado del correo institucional (ver entrega/referencias.md).</t>
+          <t>No se confirmó el tipo de enlace con el que se comparten las hojas (pregunta P2) ni si el tenant permite enlaces "Cualquier persona" (pregunta para TI). Ver amenaza T1.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Si el documento no existe internamente, registrar como brecha documental y recomendar su creación, o referenciar el apartado correspondiente del Código de Ética y Buen Gobierno si lo cubre.</t>
+          <t>Eliminar los enlaces amplios existentes y compartir solo con personas específicas; si los PAT deben registrar disponibilidad, usar un archivo aparte sin datos de terceros.</t>
         </is>
       </c>
     </row>
@@ -649,12 +699,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Seguridad (ISO 27001 / M365)</t>
+          <t>Correos Institucionales</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>La automatización usa exclusivamente herramientas ya autorizadas por la Universidad (O365, Power Automate, Power BI) con controles del proveedor.</t>
+          <t>Los avisos a profesores se envían desde la cuenta institucional de la coordinadora, no desde cuentas personales.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -664,12 +714,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>La restricción explícita del cliente (Ficha de Caracterización, Taller 0) exige que la automatización use únicamente herramientas ya autorizadas por la Universidad (Office 365, Power Automate, Power BI). Además, la política de datos personales (Num. 6-C) permite subcontratar el tratamiento a un "Encargado" externo (en este caso, Microsoft) siempre que se exijan medidas de seguridad apropiadas — condición que Microsoft 365 cubre mediante su marco contractual de cumplimiento (Data Protection Addendum / Microsoft Trust Center).</t>
+          <t>Confirmado con la cliente (Taller 4, supuestos): los avisos se envían por Exchange Online / Outlook con dominio @unisabana.edu.co, que exige autenticación de Microsoft 365.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Verificar y documentar que exista (o se suscriba) la cláusula o contrato de transmisión de datos personales con Microsoft exigido por el artículo 25 del Decreto 1377 de 2013 para encargados del tratamiento.</t>
+          <t>Mantener; enviar siempre desde la cuenta institucional y no reenviar a cuentas personales.</t>
         </is>
       </c>
     </row>
@@ -679,12 +729,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Seguridad (ISO 27001)</t>
+          <t>Correos Institucionales</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Existen logs de auditoría de quién accede/modifica horarios y resultados de la encuesta.</t>
+          <t>Las respuestas de los profesores (acepta / rechaza) quedan registradas de forma trazable.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -694,12 +744,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft 365 ofrece de forma nativa un registro de auditoría unificado (Microsoft Purview Audit) que puede capturar accesos y cambios en SharePoint, pero no se confirmó con el cliente si está habilitado, con qué periodo de retención, ni si cubre específicamente las listas del Repositorio de Programación.</t>
+          <t>Hoy las respuestas llegan al buzón de la coordinadora y no se registran en la Hoja de Asignación PAT (Taller 4, H5). Quedan en Exchange, pero dispersas. Ver amenaza T6. Corrige el antiguo ítem #5, que se había marcado Cumple con base en Power Automate, que hoy no se usa en este proceso.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Confirmar con el área de TI institucional la activación del registro de auditoría de Microsoft Purview sobre el sitio de SharePoint del proceso, con una política de retención de al menos 1 año.</t>
+          <t>Registrar cada respuesta en la Hoja de Asignación PAT (fecha, profesor, decisión) y archivar los correos en una carpeta de Outlook de la encuesta.</t>
         </is>
       </c>
     </row>
@@ -709,12 +759,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Retención</t>
+          <t>Correos Institucionales</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Existe política de retención y eliminación de horarios y respuestas de la encuesta una vez cumplida su finalidad.</t>
+          <t>Existe un reglamento o política publicada sobre el uso adecuado del correo institucional.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -724,12 +774,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>La política institucional (Num. 9) exige suprimir los datos personales una vez cumplida su finalidad, salvo obligación legal, pero no define plazos concretos para este proceso ni se confirmó que exista una regla de retención/eliminación automática configurada en SharePoint o Power Platform para los horarios y respuestas de la encuesta.</t>
+          <t>No se encontró un reglamento público específico sobre el uso del correo institucional (ver referencias.md).</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Definir un plazo concreto de conservación (p. ej. hasta el cierre del periodo de acreditación correspondiente) y configurar una política de retención/eliminación automática en Microsoft Purview sobre las listas de SharePoint del proceso.</t>
+          <t>Preguntar a TI si existe un documento interno; si no, referenciar el Código de Ética y Buen Gobierno o recomendar su creación.</t>
         </is>
       </c>
     </row>
@@ -739,12 +789,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Registro de Bases de Datos</t>
+          <t>Seguridad (ISO 27001)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>La base generada por el proceso (horarios + respuestas) está incluida en el Registro Nacional de Bases de Datos (RNBD) de la Universidad, si aplica.</t>
+          <t>La cuenta institucional de la coordinadora, que da acceso a SIGA, a las hojas y al buzón, usa autenticación multifactor (MFA).</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -754,12 +804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>El documento de política de tratamiento de datos disponible públicamente (vigente desde 2013) no menciona el Registro Nacional de Bases de Datos (RNBD, Decreto 886 de 2014, posterior a esa versión del documento); no se confirmó con el cliente si la base generada por este proceso (u otra base instituticional que la contenga) está inscrita en el RNBD de la Superintendencia de Industria y Comercio.</t>
+          <t>La cuenta usa la autenticación de Microsoft 365 (Entra ID). No se confirmó si el MFA es obligatorio (pregunta P3). Ver amenaza T2 (riesgo Alto).</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Verificar con la Dirección General Administrativa (área responsable general del tratamiento según la política) si la base de datos del proceso está cubierta por el registro RNBD institucional vigente.</t>
+          <t>Confirmar con TI y, si no está activo, habilitar MFA para la cuenta.</t>
         </is>
       </c>
     </row>
@@ -769,12 +819,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Roles y Responsabilidades</t>
+          <t>Seguridad (ISO 27001)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Estudiantes/docentes conocen el canal institucional para ejercer derechos ARCO sobre sus datos en este proceso.</t>
+          <t>Los datos del proceso se tratan solo en servicios institucionales cuyo proveedor está vinculado como Encargado del tratamiento.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -784,12 +834,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>La política institucional define el procedimiento formal para ejercer los derechos de acceso, actualización, rectificación y supresión (Num. 5), pero no se evidenció que la comunicación del proceso de encuesta informe a estudiantes y profesores sobre este canal específico ni sobre qué área (Dirección de Registro Academico / Dirección de Desarrollo Humano, según la tabla de áreas encargadas de la política) es la responsable para este caso.</t>
+          <t>Las hojas y el correo están en el tenant Microsoft 365 de la universidad (confirmado, Taller 4). La política (Num. 6-C) permite usar un Encargado si se le exigen medidas de seguridad, pero no se confirmó el contrato de transmisión de datos con Microsoft que pide el Decreto 1377 de 2013, art. 25. Las exportaciones locales (D1) quedan fuera de ese servicio. Corrige el antiguo ítem #7, que evaluaba un requisito de la solución propuesta y no un control actual.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Referenciar en la notificación el procedimiento de PQR de la política institucional y aclarar cuál es el área encargada (Registro Académico para estudiantes, Desarrollo Humano para profesores) según la tabla de responsables de la política.</t>
+          <t>Pedir a TI la evidencia del contrato o adenda de protección de datos con Microsoft; no guardar exportaciones fuera de OneDrive.</t>
         </is>
       </c>
     </row>
@@ -799,27 +849,177 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Seguridad (ISO 27001)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Existe registro de auditoría de quién accede o modifica las hojas.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft 365 ofrece un registro de auditoría unificado (Microsoft Purview Audit) que cubre OneDrive, pero no se confirmó si está activo ni con qué retención (pregunta P5).</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar con TI la activación del registro de auditoría y su retención.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Seguridad (ISO 27001)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Las hojas tienen respaldo y existe una persona de respaldo capaz de operar el proceso (continuidad).</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Cada hoja es una instancia única sin respaldo independiente (Taller 4, H3) y el proceso depende de una sola persona (H6). OneDrive guarda historial de versiones y papelera de reciclaje por defecto, pero no hay procedimiento de continuidad. Ver amenaza T4 (riesgo Alto).</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Documentar el procedimiento, designar una persona de respaldo y mover las hojas a un sitio de SharePoint del área.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Retención</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Existe un plazo definido para conservar y borrar las hojas y las exportaciones de SIGA una vez cumplida la finalidad.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>La política (Num. 9) exige suprimir los datos cuando se cumple la finalidad, pero no define plazos para este proceso. No se confirmó cuánto tiempo se conservan las hojas ni si las exportaciones se borran del equipo (pregunta P4). Ver amenaza T3.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Definir un plazo (p. ej. hasta el cierre del ciclo de autoevaluación) y borrar las exportaciones locales apenas se carguen a las hojas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Registro de Bases de Datos</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Las bases que alimentan el proceso (datos de estudiantes y empleados) están inscritas en el Registro Nacional de Bases de Datos (RNBD).</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>La política publicada (2013) es anterior al Decreto 886 de 2014 y no menciona el RNBD. No se confirmó la inscripción (pregunta P6).</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Verificar con la Dirección General Administrativa si las bases de estudiantes y empleados están inscritas en el RNBD de la SIC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Roles y Responsabilidades</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>La universidad tiene una política de tratamiento de datos publicada que designa un responsable y las áreas encargadas por tipo de dato.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>✅ Cumple</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Política de Tratamiento de Datos Personales de la Universidad de La Sabana (vigente desde el 19 de agosto de 2013): designa al Director General Administrativo como responsable y asigna áreas encargadas (Registro Académico para estudiantes, Desarrollo Humano para empleados).</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar que la versión publicada sigue vigente y citarla en la plantilla de aviso (ítem 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>Aseguramiento de la Calidad (CNA)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>La información generada por el proceso (participación, resultados de la encuesta) se consolida con trazabilidad y calidad suficientes para soportar los procesos de autoevaluación y acreditación institucional.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>La información del proceso (muestra, clases aplicadas, participación) se consolida con trazabilidad suficiente para la autoevaluación institucional.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>⚠️ Parcial</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>El Acuerdo 01 de 2025 del CESU (Lineamientos CNA, Factor 4 – Sistema Interno de Aseguramiento de la Calidad, Característica 13) exige que la institución consolide información veraz y actualizada para sus procesos de autoevaluación, y el propio informe del Taller 5 (Seguridad) señala que esta encuesta es insumo directo del proceso de acreditación institucional. Dado que el almacén actual (SharePoint Lists / Excel) aún no tiene confirmados los controles de acceso, auditoría y retención de los ítems 4, 8 y 9 de este checklist, no se puede garantizar plenamente la integridad de esta información de cara a un proceso de acreditación.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Cerrar primero las brechas de control de acceso, auditoría y retención (ítems 4, 8 y 9); una vez cerradas, documentar explícitamente cómo los datos de esta encuesta alimentan el Sistema Interno de Aseguramiento de la Calidad para el próximo ciclo de autoevaluación CNA.</t>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>El Acuerdo 01 de 2025 del CESU (Factor 4, Característica 13) exige información veraz y actualizada para la autoevaluación. Con hojas sin respaldo, sin control de cambios y respuestas sin registrar (ítems 5, 8, 12 y 13) no se puede reconstruir cómo se armó la muestra de un año.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar primero las brechas de acceso, registro de respuestas y continuidad; luego documentar cómo los resultados de la encuesta alimentan la autoevaluación.</t>
         </is>
       </c>
     </row>
@@ -834,14 +1034,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,275 +1071,460 @@
           <t>Nivel de Prioridad</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ítem del checklist</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consentimiento</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia aviso de privacidad específico del proceso en la notificación a estudiantes/profesores.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Medio</t>
+          <t>No se confirmó quién tiene acceso a las hojas con datos personales en OneDrive (amenaza T1).</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Incluir aviso de privacidad breve con la finalidad puntual del tratamiento en la notificación del flujo.</t>
+          <t>Revisar "Administrar acceso" en cada hoja y dejar solo a la coordinadora y a su persona de respaldo.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Consentimiento</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>No se referencia el canal institucional de PQR de datos personales en la comunicación del proceso.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Medio</t>
+          <t>No se confirmó el tipo de enlace con el que se comparten las hojas (amenaza T1).</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Agregar el canal de PQR y enlace a la política vigente al pie de la notificación.</t>
+          <t>Eliminar los enlaces amplios existentes y compartir solo con personas específicas; si los PAT deben registrar disponibilidad, usar un archivo aparte sin datos de terceros.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Protección de Datos (Horarios)</t>
+          <t>Seguridad (ISO 27001)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No se confirmó que los horarios cruzados desde SIGA se usen únicamente para la encuesta y no se reutilicen en otros reportes.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Medio</t>
+          <t>No se confirmó MFA en la cuenta que concentra el acceso a todo el proceso (amenaza T2).</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Documentar explícitamente el alcance de uso de los horarios cruzados y verificar ausencia de reutilización.</t>
+          <t>Confirmar con TI y, si no está activo, habilitar MFA para la cuenta.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Protección de Datos (Horarios)</t>
+          <t>Seguridad (ISO 27001)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>El acceso al Repositorio de Programación en SharePoint no tiene confirmada una matriz de roles y permisos restringida.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+          <t>Las hojas no tienen respaldo independiente y el proceso depende de una sola persona (amenaza T4).</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Definir y documentar una matriz de roles (RBAC) limitada al equipo de Automatización y al Coordinador de Encuestas.</t>
+          <t>Documentar el procedimiento, designar una persona de respaldo y mover las hojas a un sitio de SharePoint del área.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Correos Institucionales</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No existe reglamento o política publicada sobre el uso adecuado del correo institucional.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No hay plazo de conservación ni borrado de hojas y exportaciones locales (amenaza T3).</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Registrar como brecha documental y recomendar su creación, o referenciar el Código de Ética y Buen Gobierno si aplica.</t>
+          <t>Definir un plazo (p. ej. hasta el cierre del ciclo de autoevaluación) y borrar las exportaciones locales apenas se carguen a las hojas.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Seguridad (ISO 27001 / M365)</t>
+          <t>Consentimiento</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>No se confirmó la activación del registro de auditoría de Microsoft Purview sobre el sitio de SharePoint del proceso.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Alto</t>
+          <t>Los avisos a profesores no incluyen un aviso de privacidad con la finalidad del tratamiento.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Confirmar con TI institucional la activación del log de auditoría con retención de al menos 1 año.</t>
+          <t>Crear una plantilla de aviso con un párrafo breve de finalidad (programación de la encuesta) y el fundamento (Ley 1581 de 2012 y política institucional).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
-        </is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Retención</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No existe política de retención/eliminación automática configurada para horarios y respuestas de la encuesta.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+          <t>No está documentado que los datos exportados de SIGA se usen solo para la encuesta.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Definir plazo de conservación y configurar regla de retención en Microsoft Purview.</t>
+          <t>Dejar por escrito, en la primera pestaña de cada hoja, la finalidad del archivo y que no debe usarse para otros fines.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Registro de Bases de Datos</t>
+          <t>Protección de Datos</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No se confirmó si la base del proceso está cubierta por el registro RNBD institucional vigente.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+          <t>Las exportaciones de SIGA se cargan a las hojas sin minimizar columnas (amenaza T7).</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Verificar con la Dirección General Administrativa la cobertura del RNBD institucional sobre esta base.</t>
+          <t>Definir la lista mínima de columnas (p. ej. código, programa, semestre, clase, horario, correo del profesor) y borrar las demás antes de cargar a las hojas.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Roles y Responsabilidades</t>
+          <t>Correos Institucionales</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>La comunicación del proceso no informa el área responsable específica para ejercer derechos ARCO en este caso.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>Las respuestas de los profesores no quedan registradas de forma estructurada (amenaza T6).</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Referenciar en la notificación el área encargada (Registro Académico / Desarrollo Humano) según la política institucional.</t>
+          <t>Registrar cada respuesta en la Hoja de Asignación PAT (fecha, profesor, decisión) y archivar los correos en una carpeta de Outlook de la encuesta.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Seguridad (ISO 27001)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó el contrato de transmisión de datos con Microsoft como Encargado; las exportaciones locales quedan fuera del servicio.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Pedir a TI la evidencia del contrato o adenda de protección de datos con Microsoft; no guardar exportaciones fuera de OneDrive.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Seguridad (ISO 27001)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó la activación del registro de auditoría de Microsoft Purview.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar con TI la activación del registro de auditoría y su retención.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Registro de Bases de Datos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó la inscripción en el RNBD de las bases que alimentan el proceso.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Verificar con la Dirección General Administrativa si las bases de estudiantes y empleados están inscritas en el RNBD de la SIC.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Aseguramiento de la Calidad (CNA)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>La integridad y trazabilidad de los datos de la encuesta para el proceso de acreditación institucional no está garantizada mientras persistan las brechas de acceso, auditoría y retención.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>La trazabilidad de la muestra no es suficiente para soportar la autoevaluación institucional.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Cerrar primero las brechas de acceso, auditoría y retención; luego documentar la trazabilidad de estos datos hacia el Sistema Interno de Aseguramiento de la Calidad.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar primero las brechas de acceso, registro de respuestas y continuidad; luego documentar cómo los resultados de la encuesta alimentan la autoevaluación.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Consentimiento</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Los avisos del proceso no informan el canal de PQR ni el área responsable de los datos.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Incluir al pie de la plantilla el canal protecciondedatos@unisabana.edu.co y el enlace a la política vigente.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Correos Institucionales</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>No se encontró un reglamento público sobre el uso del correo institucional.</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Preguntar a TI si existe un documento interno; si no, referenciar el Código de Ética y Buen Gobierno o recomendar su creación.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
